--- a/TBM Organization Parameters.xlsx
+++ b/TBM Organization Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/MicroDrive/SparrowGIT/TBM_Organization_Parameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{C91E8DA0-4003-1C4F-8298-E14445E5B480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DE7FAA-5AB2-F149-AD05-3E0CA9E77BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20360" tabRatio="813" firstSheet="18" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" tabRatio="813" firstSheet="25" activeTab="40" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TBM" sheetId="7" r:id="rId1"/>
@@ -83,7 +83,6 @@
     <definedName name="Special">[1]types!$A$169:$A$177</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -100,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4891" uniqueCount="1306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4898" uniqueCount="1310">
   <si>
     <t>Latitude</t>
   </si>
@@ -2530,9 +2529,6 @@
   </si>
   <si>
     <t>Spanish, English,</t>
-  </si>
-  <si>
-    <t>TBM, TBMCV, TBMK,</t>
   </si>
   <si>
     <t>Language Not Available on WiFi Box
@@ -3682,12 +3678,6 @@
     <t>Komo</t>
   </si>
   <si>
-    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMSL,</t>
-  </si>
-  <si>
-    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMKB</t>
-  </si>
-  <si>
     <t>Tanzania - Oloobilin</t>
   </si>
   <si>
@@ -3832,60 +3822,21 @@
     <t xml:space="preserve">Akan-Akuapem-Twi, Spanish, English, Ewe, isiZulu, Swahili, </t>
   </si>
   <si>
-    <t>Afenmai, Ake-Levbu, Akoko, Akwai, Akyem, Amo, Anaguta, Ankwe, Annang, Bagim, Bajju, Bakhayo, Baniwa, Banjara, Bengali, Banyore, Bono, Bora, Buli, Bwai, Calabar, Chamba, Chawai, Chekosi, Chumburu, Creole, Criolo, Demark, Desano, Doemak, Edo, Efik, Eggon, Emai, Esan, Etsako, Etuno, Fante, Frafra, French, Fulfude (Fulani), Ga/Adangbe, Goemai, Gonja, Grune, Here, Hindi, Ibibio, Idoma, Igala, Igbanke, Igbo, Ijaw, Imua, Irigwe, Isoko, Itsekiri, Jarawa, Jukun, Kanjaga, Kannada, Kofia, Komo, Konkomba, Koro, Kotokoli, Krobo, Kulere, Kwal, Lemoro, Lubukusu, Lugwere, Lusamya, Luyole, Magogo, Marachi, Marathi, Marubo, Mernian, Minchika, Miranha, Miranhas, Mupun, Mura, Mushere, Mwaghavul, Nanuni, Nawuri, Nchumburu, Ngas, Nhengatu, Ntrubo, Ntu-Mbusor, Ogoja, Okpameri, Okpe, Oniyan, Oron, Other, Piraha, Piratapuyo, Pyem, Quan, Rindere, Ron, Rukuba (Bache), Satere-Mawe, Sekpele, Selee, Sisaali, Sisaala_Tumulung, Siwu, Skaryanas, Stiwa, Talni, Tamil, Tarok, Telugu, Tenharim, Ticuna, Tucano, Tula, Tuwuli, Tuyuca, Twi, Urhobo, Waali, Wamba, Wayway, Youm,</t>
-  </si>
-  <si>
-    <t>Acholi, Adele, Agutaynen, Akan-Akuapem-Twi, Akan-Asante, Akan-Fante, Alangan, Alur, Antipolo Ifugao, Anufo, Apalai, Apinaye, Apurina, Ateso, Ayangan, Ayangan Ifugao, Ayta Abellen, Ayta Mag antsi, Ayta Mag Indi, Bakairi, Bantoanon, Bekwarra, Berom, Bete-Bendi, Bicolano Central, Bikol Rinconada, Bimoba, Birifor-Southern, Bisa, Bokobaru-Sim, Borana, Bororo, Bukidnon,  Buli, Bura, Busa-Bisa, Canela, Canela, Cebuano, Central Ifugao, Central Subanen, Chumburung, Culina, Daasanach, Dagaare, Dagbani, Dhopadhola, Duruma, Dza, Ebira, Embu, Ewe, Finallig, Frafra, Ga, Gikyode, Giryama, Guajajara, Hanga, Hanunoo, Hausa, Hiligaynon, Hixkaryana, Inakeanon, Ilchamus, Ilokano, Jamamadi, Jarawara, Kaapor, Kadiweu, Kagayanen, Kaingang, Kaiwa, Kakwa, Kalagan Eastern, Kalanguya, Kalenjin, Kalinga Butbut, Kalinga Lubuagan, Kalinga Majukayong, Kamayura, Kamba, Kankanaey, Karaja, Karimojong, Kasem, Kayabi, Kayapo, Kebu, Kikuyu, Kinaray, Kisii, Kiswahili, Kiwilwana, Kolibugan, Koma, Kono, Konkomba-Likoonli, Konkomba-Likpakpaaln, Koronadal, Krio, Kulina, Kumam, Kupsapiny, Kuranko, Kusaal, Lango, Lelemi, Limba West, Lubukusu, Lubwisi, Luganda,  Lugbara, Lugungu, Lugwere, Luhya, Lukakamega, Lumasaba, Lunyankore, Lunyore, Luo, Lusamya, Lusoga, Maasai, Macushi, Madi, Mampruli, Manchineri, Mangali, Marakwet, Maxakali, Mbya Guarani, Mende, Meru, Minonuvu, Munduruku, Nadeb, Nambikuara (Southern), Nawuri, Nkonya, Ntrubo, Nzema, Obolo, Okphela, Orma, Paasaal, Pahanan, Palawano, Palikur, Pampangan, Pangasinan, Paranan, Parecis, Paumari, Pokoot, Portuguese, Rikbaktsa, Romblomanon, Runyoro-Rutoro, Sabaot, Samareno, Sambal, Sambali, Samburu, Sarangani, Satere-Mawe, Sekpele, Selee, Shanga, Sinama, Sisaala-Tumulung, Siwu, Suba, Tadyawan, Tagalog, Taita, Tampulma, Tawbuid, Tboli, Tenharim, Terena, Tharaka, Themne, Tiv, Tukano, Turkana, Tuwuli, Tuwali Ifugao, Tyap, UaiUai, Vagla, Wali, Xavante, Yakan, Yoruba,</t>
-  </si>
-  <si>
-    <t>Acholi, Adele, Afrikaans, Akan-Akuapem-Twi, Akan-Asante, Akan-Fante, Alur, Anufo, Ateso, Bimoba, Birifor-Southern, Borana, Buli, Canela, Cebuano, Chumburung, Daasanach, Dagaare, Dagbani, Dhopadhola, Duruma, English, Ewe, Ga, Gikyode, Giryama, Guajajara, Hanga, Ilchamus, IsiXhosa, IsiZulu, Kaapor, Kadiweu, Kakwa, Kalenjin, Kamba, Karimojong, Kasem, Kayabi, Kayapo, Kebu, Kikamba, Kimeru, Kiswahili, Kiwihwana, Koma, Konkomba-Likoonli, Konkomba-Likpakpaaln, Krio, Kumam, Kupsapiny, Kusaal, Lango, Lelemi, Lubwisi, Luganda, Lugbara, Lumasaaba, Lunyore, Luo, Lusoga, Maasai, Madi, Mampruli, Mende, Meru, Ndebele Northern, Ndebele Southern, Nkonya, Nzema, Paasaal, Parecis, Polkoot, Portuguese, Runyankore, Runyoro-Rutoro, Sabaot, Samburu, Sesotho, Sesotho sa Leboa, Setswana, Sisaala-Tumulung, siSwati, Spanish, Suba, Taita, Tampulma, Tharaka, Themne, Turkana, Vagla, Wali, Xitsonga,</t>
-  </si>
-  <si>
-    <t>Acholi, Afrikaans, Akan-Akuapem-Twi, Akan-Asante, Anufo, Dagbani, English, Ewe, IsiXhosa, IsiZulu, Kasem, Kiswahili, Konkomba-Likoonli, Konkomba-Likpakpaaln, Krio, Kusaal, Luganda, Mende, Ndebele Northern, Runyankore, Setswana, Setswana, Sisaala-Tumulung, siSwati, Themne,</t>
-  </si>
-  <si>
     <t>Akan-Akuapem-Twi, English, Kiswahili, Portuguese,</t>
   </si>
   <si>
-    <t>Akan-Akuapem-Twi, Akan-Asante, English, Portuguese, Cebuano</t>
-  </si>
-  <si>
     <t>Akan-Akuapem-Twi, Akan-Asante, Ewe, Kiswahili, Krio, Luganda, Mende, Portuguese, Themne,</t>
   </si>
   <si>
     <t>Akan-Akuapem-Twi, Akan-Asante, Ewe, Kiswahili, Krio, Luganda, Mende, Ndebele Northern, Portuguese, Themne,</t>
   </si>
   <si>
-    <t>Akan-Asante, Kiswahili, Luganda, Portuguese, Cebuano</t>
-  </si>
-  <si>
-    <t>Afrikaans, Akan-Asante, Cebuano, IsiXhosa, IsiZulu, Kiswahili, Krio, Luganda, Mende, Portuguese, Setswana, siSwati, Themne,</t>
-  </si>
-  <si>
     <t>Canela, Ende, English, Guajajara, Kadiweu, Kaapor, Kayabi, Kayapo, Kono, Krio, Kuranko, Limba West, Parecis, Themne,</t>
   </si>
   <si>
-    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMPB, TBMKB, TBMSL, TBMGN, TBMKN,</t>
-  </si>
-  <si>
-    <t>TBM, TBMCV, TBMKA, TBMK, TBMSL, TBMKN,</t>
-  </si>
-  <si>
-    <t>Acholi, Adele, Afrikaans, Akan-Akuapem-Twi, Akan-Asante, Akan-Fante, Alur, Anufo, Ateso, Bimoba, Birifor-Southern, Borana, Buli, Canela, Cebuano, Chumburung, Daasanach, Dagaare, Dagbani, Dhopadhola, Duruma, English, Ewe, Fullah, Ga, Gikyode, Giryama, Guajajara, Hanga, Ilchamus, IsiXhosa, IsiZulu, Kaapor, Kadiweu, Kakwa, Kalenjin, Kamba, Karimojong, Kasem, Kayabi, Kayapo,  Kebu, Kikamba, Kimeru, Kiswahili, Kiwihwana, Koma, Kono, Konkomba-Likoonli, Konkomba-Likpakpaaln, Krio, Kumam, Kupsapiny, Kuranko, Kusaal, Lango, Lelemi, Limba West, Lubwisi, Luganda, Lugbara, Lumasaaba, Lunyore, Luo, Lusoga, Maasai, Madi, Mampruli, Mende, Meru, Ndebele Northern, Ndebele Southern, Nkonya, Nzema, Paasaal, Parecis, Polkoot, Portuguese, Runyankore, Runyoro-Rutoro, Sabaot, Samburu, Sisaala-Tumulung, siSwati, Sesotho, Sesotho sa Leboa, Setswana, Spanish, Suba, Taita, Tampulma, Tharaka, Themne, Turkana, Vagla, Wali, Xitsonga,</t>
-  </si>
-  <si>
     <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMPB, TBMKB, TBMSL, TBMGN, TBMSA, TBMKN,</t>
   </si>
   <si>
-    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMKB, TBMSL, TBMSA, TBMKN,</t>
-  </si>
-  <si>
-    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMSL, TBMSA, TBMKN,</t>
-  </si>
-  <si>
-    <t>TBM, TBMCV, TBMKA, TBMK, TBMSA, TBMSL, TBMGN, TBMKN,</t>
-  </si>
-  <si>
     <t>The Bucket Ministry Sao Jose Operario</t>
   </si>
   <si>
@@ -4019,6 +3970,66 @@
   </si>
   <si>
     <t>Indiana</t>
+  </si>
+  <si>
+    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMPB, TBMKB, TBMSL, TBMGN, TBMKN, TBMCJ, TBMNJ,</t>
+  </si>
+  <si>
+    <t>TBM, TBMCV, TBMKA, TBMK, TBMSL, TBMKN, TBMCJ, TBMNJ,</t>
+  </si>
+  <si>
+    <t>TBM, TBMCV, TBMK, TBMCJ,</t>
+  </si>
+  <si>
+    <t>Acholi, Adele, Agutaynen, Akan-Akuapem-Twi, Akan-Asante, Akan-Fante, Alangan, Alur, Antipolo Ifugao, Anufo, Apalai, Apinaye, Apurina, Ateso, Ayangan, Ayangan Ifugao, Ayta Abellen, Ayta Mag antsi, Ayta Mag Indi, Bakairi, Bantoanon, Bekwarra, Berom, Bete-Bendi, Bicolano Central, Bikol Rinconada, Bimoba, Birifor-Southern, Bisa, Bokobaru-Sim, Borana, Bororo, Bukidnon,  Buli, Bura, Busa-Bisa, Canela, Canela, Cebuano, Central Ifugao, Central Subanen, Chumburung, Culina, Daasanach, Dagaare, Dagbani, Dhopadhola, Duruma, Dza, Ebira, Eggon, Embu, Ewe, Finallig, Frafra, Ga, Gikyode, Giryama, Guajajara, Hanga, Hanunoo, Hausa, Hiligaynon, Hixkaryana, Idoma, Igbo, Igede, Inakeanon, Ilchamus, Ilokano, Irigwe, Jamamadi, Jarawara, Kaapor, Kadiweu, Kagayanen, Kaingang, Kaiwa, Kakwa, Kalagan Eastern, Kalanguya, Kalenjin, Kalinga Butbut, Kalinga Lubuagan, Kalinga Majukayong, Kamayura, Kamba, Kankanaey, Karaja, Karimojong, Kasem, Kayabi, Kayapo, Kebu, Kikuyu, Kinaray, Kisii, Kiswahili, Kiwilwana, Kolibugan, Koma, Kono, Konkomba-Likoonli, Konkomba-Likpakpaaln, Koronadal, Krio, Kulina, Kumam, Kupsapiny, Kuranko, Kusaal, Kutep, Lango, Lelemi, Limba West, Lubukusu, Lubwisi, Luganda,  Lugbara, Lugungu, Lugwere, Luhya, Lukakamega, Lumasaba, Lunyankore, Lunyore, Luo, Lusamya, Lusoga, Maasai, Macushi, Madi, Mampruli, Manchineri, Mangali, Marakwet, Maxakali, Mbya Guarani, Mende, Meru, Minonuvu, Munduruku, Mwaghavul, Nadeb, Nambikuara (Southern), Nawuri, Nigerian Pidgin, Nkonya, Ntrubo, Nzema, Obolo, Okphela, Orma, Paasaal, Pahanan, Palawano, Palikur, Pampangan, Pangasinan, Paranan, Parecis, Paumari, Pokoot, Portuguese, Rikbaktsa, Romblomanon, Runyoro-Rutoro, Sabaot, Samareno, Sambal, Sambali, Samburu, Sarangani, Satere-Mawe, Sekpele, Selee, Shanga, Sinama, Sisaala-Tumulung, Siwu, Suba, Tadyawan, Tagalog, Taita, Tampulma, Tawbuid, Tboli, Tenharim, Terena, Tharaka, Themne, Tiv, Tukano, Turkana, Tuwuli, Tuwali Ifugao, Tyap, UaiUai, Vagla, Wali, Xavante, Yakan, Yoruba,</t>
+  </si>
+  <si>
+    <t>Acholi, Adele, Afrikaans, Akan-Akuapem-Twi, Akan-Asante, Akan-Fante, Alur, Anufo, Ateso, Bekwarra, Berom, Bete-Bendi, Bimoba, Birifor-Southern, Borana, Buli, Bura, Canela, Cebuano, Chumburung, Daasanach, Dagaare, Dagbani, Dhopadhola, Duruma, Ebira, Eggon, English, Ewe, Fullah, Ga, Gikyode, Giryama, Guajajara, Hanga, Idoma, Igbo, Igede, Ilchamus, IsiXhosa, IsiZulu, Kaapor, Kadiweu, Kakwa, Kalenjin, Kamba, Karimojong, Kasem, Kayabi, Kayapo,  Kebu, Kikamba, Kimeru, Kiswahili, Kiwihwana, Koma, Kono, Konkomba-Likoonli, Konkomba-Likpakpaaln, Krio, Kumam, Kupsapiny, Kuranko, Kusaal, Kutep, Lango, Lelemi, Limba West, Lubwisi, Luganda, Lugbara, Lumasaaba, Lunyore, Luo, Lusoga, Maasai, Madi, Mampruli, Mende, Meru, Mwaghavul, Ndebele Northern, Ndebele Southern, Nigerian Pidgin, Nkonya, Nzema, Paasaal, Parecis, Polkoot, Portuguese, Runyankore, Runyoro-Rutoro, Sabaot, Samburu, Sisaala-Tumulung, siSwati, Sesotho, Sesotho sa Leboa, Setswana, Spanish, Suba, Taita, Tampulma, Tharaka, Themne, Turkana, Tyap, Vagla, Wali, Xitsonga, Yoruba,</t>
+  </si>
+  <si>
+    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMKB, TBMSA, TBMKN,</t>
+  </si>
+  <si>
+    <t>Afenmai, Ake-Levbu, Akoko, Akwai, Akyem, Amo, Anaguta, Ankwe, Annang, Bagim, Bajju, Bakhayo, Baniwa, Banjara, Bengali, Banyore, Bono, Bora, Buli, Bwai, Calabar, Chamba, Chawai, Chekosi, Chumburu, Creole, Criolo, Demark, Desano, Doemak, Edo, Efik, Emai, Esan, Etsako, Etuno, Fante, Frafra, French, Fulfude (Fulani), Ga/Adangbe, Goemai, Gonja, Grune, Here, Hindi, Ibibio, Igala, Igbanke, Ijaw, Imua, Isoko, Itsekiri, Jarawa, Jukun, Kanjaga, Kannada, Kofia, Komo, Konkomba, Koro, Kotokoli, Krobo, Kulere, Kwal, Lemoro, Lubukusu, Lugwere, Lusamya, Luyole, Magogo, Marachi, Marathi, Marubo, Mernian, Minchika, Miranha, Miranhas, Mupun, Mura, Mushere, Nanuni, Nawuri, Nchumburu, Ngas, Nhengatu, Ntrubo, Ntu-Mbusor, Ogoja, Okpameri, Okpe, Oniyan, Oron, Other, Piraha, Piratapuyo, Pyem, Quan, Rindere, Ron, Rukuba (Bache), Satere-Mawe, Sekpele, Selee, Sisaali, Sisaala_Tumulung, Siwu, Skaryanas, Stiwa, Talni, Tamil, Tarok, Telugu, Tenharim, Ticuna, Tucano, Tula, Tuwuli, Tuyuca, Twi, Urhobo, Waali, Wamba, Wayway, Youm,</t>
+  </si>
+  <si>
+    <t>Akan-Akuapem-Twi, Spanish, English, Ewe, isiZulu, Swahili, Hausa, Igbo, Yoruba,</t>
+  </si>
+  <si>
+    <t>Acholi, Adele, Afrikaans, Akan-Akuapem-Twi, Akan-Asante, Akan-Fante, Alur, Anufo, Ateso, Bekwarra, Berom, Bete-Bendi, Bimoba, Birifor-Southern, Borana, Buli, Bura, Canela, Cebuano, Chumburung, Daasanach, Dagaare, Dagbani, Dhopadhola, Duruma, English, Eggon, Ewe, Ga, Gikyode, Giryama, Guajajara, Hanga, Hausa, Idoma, Igbo, Igede, Ilchamus, IsiXhosa, IsiZulu, Kaapor, Kadiweu, Kakwa, Kalenjin, Kamba, Karimojong, Kasem, Kayabi, Kayapo, Kebu, Kikamba, Kimeru, Kiswahili, Kiwihwana, Koma, Konkomba-Likoonli, Konkomba-Likpakpaaln, Krio, Kumam, Kupsapiny, Kusaal, Kutep, Lango, Lelemi, Lubwisi, Luganda, Lugbara, Lumasaaba, Lunyore, Luo, Lusoga, Maasai, Madi, Mampruli, Mende, Meru, Mwaghavul, Ndebele Northern, Ndebele Southern, Nigerian Pidgin, Nkonya, Nzema, Paasaal, Parecis, Polkoot, Portuguese, Runyankore, Runyoro-Rutoro, Sabaot, Samburu, Sesotho, Sesotho sa Leboa, Setswana, Sisaala-Tumulung, siSwati, Spanish, Suba, Taita, Tampulma, Tharaka, Themne, Tiv, Turkana, Tyap, Vagla, Wali, Yoruba, Xitsonga,</t>
+  </si>
+  <si>
+    <t>Acholi, Afrikaans, Akan-Akuapem-Twi, Akan-Asante, Anufo, Berom, Dagbani, English, Ewe, Hausa, IsiXhosa, IsiZulu, Kasem, Kiswahili, Konkomba-Likoonli, Konkomba-Likpakpaaln, Krio, Kusaal, Luganda, Mende, Ndebele Northern, Runyankore, Setswana, Setswana, Sisaala-Tumulung, siSwati, Themne, Tiv, Yoruba,</t>
+  </si>
+  <si>
+    <t>Akan-Akuapem-Twi, Akan-Asante, Berom, English, Portuguese, Cebuano</t>
+  </si>
+  <si>
+    <t>Afrikaans, Akan-Asante, Cebuano, IsiXhosa, IsiZulu, Kiswahili, Krio, Luganda, Mende, Portuguese, Setswana, siSwati, Themne, Yoruba,</t>
+  </si>
+  <si>
+    <t>Igede</t>
+  </si>
+  <si>
+    <t>Kutep</t>
+  </si>
+  <si>
+    <t>Nigerian Pidgin</t>
+  </si>
+  <si>
+    <t>TBM, TBMCV, TBMK, TBMBS, TBMQS, TBMQN, TBMM, TBMBW, TBMBSJ,  TBMCJ,</t>
+  </si>
+  <si>
+    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMN, TBMSA, TBMBS, TBMQS, TBMQN, TBMM, TBMBW, TBMKB, TBMSL, TBMSA, TBMKN, TBMBSJ, TBMCJ, TBMNJ, </t>
+  </si>
+  <si>
+    <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMSL, TBMSA, TBMKN, TBMCJ, TBMNJ,</t>
+  </si>
+  <si>
+    <t>TBM, TBMCV, TBMKA, TBMK, TBMSA, TBMSL, TBMGN, TBMSA, TBMKN, TBMCJ, TBMNJ,</t>
+  </si>
+  <si>
+    <t>Akan-Asante, Cebuano, Kiswahili, Luganda, Portuguese, Igbo, Yoruba,</t>
   </si>
 </sst>
 </file>
@@ -4331,7 +4342,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4428,6 +4439,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -5161,7 +5175,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>277</v>
@@ -5688,7 +5702,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>1274</v>
+        <v>1258</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -5713,7 +5727,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>117</v>
@@ -5730,7 +5744,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="29"/>
@@ -5741,7 +5755,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="47" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="29"/>
@@ -5752,7 +5766,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="47" t="s">
-        <v>1273</v>
+        <v>1257</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="29"/>
@@ -5795,7 +5809,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4914AC-81CB-46C7-BD71-CF158ABA186A}">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -5922,7 +5936,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1269</v>
+        <v>1253</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>291</v>
@@ -6377,6 +6391,39 @@
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C78" s="15"/>
+      <c r="D78" s="53" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D79" s="53" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D80" s="53" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D81" s="53" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D82" s="53" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D83" s="26" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D84" s="53" t="s">
+        <v>506</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:C78">
@@ -7493,7 +7540,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -7524,7 +7571,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="40" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C3" t="s">
         <v>469</v>
@@ -7535,602 +7582,602 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="40" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="40" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="40" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="40" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="40" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="40" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="40" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="40" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="40" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="40" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="40" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="40" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="40" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="40" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="40" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="40" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="40" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="40" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="40" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="40" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="40" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="40" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="40" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="40" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="40" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="40" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="40" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="40" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="40" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="40" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="40" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="40" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="40" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="40" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="40" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="40" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="40" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="40" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="40" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="40" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="40" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="40" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="40" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="40" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="40" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="40" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="40" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="40" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="40" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="40" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="40" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="40" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="40" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="40" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="40" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="40" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="40" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="40" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="40" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="40" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="40" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="40" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="40" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="40" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="40" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="40" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="40" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="40" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="40" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="40" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="40" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="40" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="40" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="40" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="40" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="40" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="40" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="40" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="40" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="40" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="40" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="40" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="40" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="40" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="40" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="40" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="40" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="40" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="40" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="40" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="40" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="40" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="40" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="40" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="40" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="40" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="40" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="40" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="40" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="40" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="40" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="40" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="40" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="40" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="40" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="40" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="40" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="40" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="40" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="40" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="40" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="40" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="40" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="40" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="40" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="40" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="40" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -8159,7 +8206,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C1" s="50"/>
       <c r="D1" s="50"/>
@@ -8190,10 +8237,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C3" t="s">
         <v>1019</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1020</v>
       </c>
       <c r="D3" t="s">
         <v>342</v>
@@ -8204,7 +8251,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C4" t="s">
         <v>500</v>
@@ -8218,10 +8265,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C5" t="s">
         <v>1022</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1023</v>
       </c>
       <c r="D5" t="s">
         <v>103</v>
@@ -8232,7 +8279,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C6" t="s">
         <v>502</v>
@@ -8246,7 +8293,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C7" t="s">
         <v>340</v>
@@ -8260,7 +8307,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C8" t="s">
         <v>469</v>
@@ -8271,7 +8318,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C9" t="s">
         <v>587</v>
@@ -8282,7 +8329,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
@@ -8293,17 +8340,17 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
   </sheetData>
@@ -8516,7 +8563,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C1" s="50"/>
       <c r="D1" s="50"/>
@@ -8525,7 +8572,7 @@
         <v>495</v>
       </c>
       <c r="G1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -8533,7 +8580,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>69</v>
@@ -8547,13 +8594,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E3" t="s">
         <v>407</v>
@@ -8561,10 +8608,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D4" s="27" t="s">
         <v>103</v>
@@ -8575,13 +8622,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E5" t="s">
         <v>409</v>
@@ -8589,121 +8636,121 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -8741,7 +8788,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -8827,7 +8874,7 @@
         <v>246</v>
       </c>
       <c r="D7" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -8968,7 +9015,7 @@
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="3"/>
       <c r="C23" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
@@ -9905,7 +9952,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -9922,7 +9969,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="18"/>
@@ -9932,7 +9979,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="B5" s="3"/>
       <c r="D5" s="18"/>
@@ -9942,7 +9989,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="18"/>
@@ -9996,7 +10043,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -10021,7 +10068,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -10038,7 +10085,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="18" t="s">
@@ -10050,7 +10097,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B5" s="3"/>
       <c r="D5" s="18" t="s">
@@ -10062,7 +10109,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="18" t="s">
@@ -10074,7 +10121,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" s="4" t="s">
@@ -10086,7 +10133,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" s="4" t="s">
@@ -10095,7 +10142,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" s="4" t="s">
@@ -10104,64 +10151,64 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B10" s="3"/>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B11" s="3"/>
       <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B13" s="2"/>
       <c r="D13" s="18"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B19" s="3"/>
     </row>
@@ -10226,7 +10273,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -10251,7 +10298,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -10268,7 +10315,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D4" t="s">
         <v>386</v>
@@ -10279,7 +10326,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D5" t="s">
         <v>387</v>
@@ -10290,7 +10337,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D6" t="s">
         <v>388</v>
@@ -10301,7 +10348,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
@@ -10312,7 +10359,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D8" t="s">
         <v>103</v>
@@ -10320,7 +10367,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -10328,32 +10375,32 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -10583,7 +10630,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>1261</v>
+        <v>1245</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -10608,7 +10655,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>1262</v>
+        <v>1246</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>117</v>
@@ -10900,7 +10947,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -10925,13 +10972,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E3" t="s">
         <v>407</v>
@@ -10939,13 +10986,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="34" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E4" t="s">
         <v>408</v>
@@ -10953,13 +11000,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C5" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D5" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E5" t="s">
         <v>409</v>
@@ -10967,13 +11014,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="34" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E6" s="40" t="s">
         <v>480</v>
@@ -10981,13 +11028,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="34" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E7" s="40" t="s">
         <v>481</v>
@@ -10995,73 +11042,73 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="40" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E8" s="40"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="40" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E9" s="40"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -11442,7 +11489,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>1275</v>
+        <v>1259</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -11451,7 +11498,7 @@
         <v>495</v>
       </c>
       <c r="G1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -11473,7 +11520,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1276</v>
+        <v>1260</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>117</v>
@@ -11490,7 +11537,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1277</v>
+        <v>1261</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="29"/>
@@ -11501,7 +11548,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1278</v>
+        <v>1262</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="29"/>
@@ -11512,7 +11559,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1279</v>
+        <v>1263</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="29"/>
@@ -11521,7 +11568,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" s="4"/>
@@ -11529,136 +11576,136 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1282</v>
+        <v>1266</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1283</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1284</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1285</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1286</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1287</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1288</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1289</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1292</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>1294</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1295</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1296</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>1297</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>1298</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>1300</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>1301</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1302</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>1303</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1304</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1305</v>
+        <v>1289</v>
       </c>
     </row>
   </sheetData>
@@ -11695,7 +11742,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -11704,7 +11751,7 @@
         <v>495</v>
       </c>
       <c r="G1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -11726,7 +11773,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -11743,7 +11790,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="4" t="s">
@@ -11755,7 +11802,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B5" s="3"/>
       <c r="D5" s="5" t="s">
@@ -11767,7 +11814,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="4" t="s">
@@ -11776,7 +11823,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" s="4" t="s">
@@ -11785,7 +11832,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" s="4" t="s">
@@ -11794,7 +11841,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" s="4" t="s">
@@ -11803,85 +11850,85 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="B21" s="3"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B23" s="3"/>
     </row>
@@ -11931,7 +11978,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -11940,7 +11987,7 @@
         <v>495</v>
       </c>
       <c r="G1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -11962,7 +12009,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -11979,7 +12026,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="4" t="s">
@@ -11991,7 +12038,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B5" s="3"/>
       <c r="D5" s="5" t="s">
@@ -12003,7 +12050,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="4" t="s">
@@ -12012,7 +12059,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" s="4" t="s">
@@ -12021,7 +12068,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="42" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" s="4" t="s">
@@ -12030,7 +12077,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" s="4" t="s">
@@ -12039,91 +12086,91 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B21" s="3"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B24" s="3"/>
     </row>
@@ -12172,7 +12219,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>1263</v>
+        <v>1247</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -12181,7 +12228,7 @@
         <v>495</v>
       </c>
       <c r="G1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -12203,7 +12250,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1264</v>
+        <v>1248</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -12220,7 +12267,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1265</v>
+        <v>1249</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="4"/>
@@ -12230,7 +12277,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
       <c r="B5" s="3"/>
       <c r="D5" s="5"/>
@@ -12240,14 +12287,14 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1267</v>
+        <v>1251</v>
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1268</v>
+        <v>1252</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" s="4"/>
@@ -21447,7 +21494,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -21456,7 +21503,7 @@
         <v>495</v>
       </c>
       <c r="G1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -21478,7 +21525,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -21495,7 +21542,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="4" t="s">
@@ -21507,7 +21554,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B5" s="3"/>
       <c r="D5" s="5" t="s">
@@ -21519,7 +21566,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="4" t="s">
@@ -21528,19 +21575,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -21612,7 +21659,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>117</v>
@@ -21629,7 +21676,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="29" t="s">
@@ -21679,7 +21726,7 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
       <c r="C8" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D8" s="4"/>
     </row>
@@ -21767,7 +21814,7 @@
     </row>
     <row r="25" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="26" spans="3:3" x14ac:dyDescent="0.2">
@@ -21864,7 +21911,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -21873,7 +21920,7 @@
         <v>495</v>
       </c>
       <c r="G1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -21895,7 +21942,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -21912,7 +21959,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="4" t="s">
@@ -21924,7 +21971,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B5" s="3"/>
       <c r="D5" s="5" t="s">
@@ -21936,7 +21983,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="4" t="s">
@@ -21945,25 +21992,25 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B10" s="3"/>
     </row>
@@ -22016,10 +22063,10 @@
         <v>799</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>1254</v>
+        <v>1290</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>1244</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -22027,7 +22074,7 @@
         <v>442</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>1255</v>
+        <v>1291</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>806</v>
@@ -22038,7 +22085,7 @@
         <v>412</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>810</v>
+        <v>1292</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>807</v>
@@ -22049,54 +22096,54 @@
         <v>414</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>810</v>
+        <v>1292</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="40" t="s">
         <v>497</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>810</v>
+        <v>1305</v>
       </c>
       <c r="C6" s="39" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="40" t="s">
         <v>498</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>810</v>
+        <v>1305</v>
       </c>
       <c r="C7" s="39" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="255" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="289" x14ac:dyDescent="0.2">
       <c r="A8" s="40" t="s">
         <v>800</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>1257</v>
+        <v>1244</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="40" t="s">
         <v>801</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>1258</v>
+        <v>1306</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -22104,7 +22151,7 @@
         <v>479</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>1193</v>
+        <v>1307</v>
       </c>
       <c r="C10" s="39" t="s">
         <v>809</v>
@@ -22115,32 +22162,32 @@
         <v>802</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>1259</v>
+        <v>1307</v>
       </c>
       <c r="C11" s="39" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="40" t="s">
         <v>803</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>1260</v>
+        <v>1308</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A13" s="39" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>1194</v>
+        <v>1295</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>1243</v>
+        <v>1296</v>
       </c>
     </row>
   </sheetData>
@@ -22155,16 +22202,16 @@
   <cols>
     <col min="1" max="1" width="45" style="40" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.5" style="40" customWidth="1"/>
+    <col min="3" max="3" width="81.83203125" style="40" customWidth="1"/>
     <col min="4" max="16384" width="8.83203125" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C1" s="40" t="s">
         <v>805</v>
@@ -22175,10 +22222,10 @@
         <v>450</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22186,10 +22233,10 @@
         <v>422</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22197,10 +22244,10 @@
         <v>423</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22208,10 +22255,10 @@
         <v>424</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22219,10 +22266,10 @@
         <v>452</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22230,10 +22277,10 @@
         <v>425</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22241,10 +22288,10 @@
         <v>426</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22252,10 +22299,10 @@
         <v>427</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22263,7 +22310,7 @@
         <v>428</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C10" s="39" t="s">
         <v>809</v>
@@ -22274,10 +22321,10 @@
         <v>429</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22285,10 +22332,10 @@
         <v>453</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22296,7 +22343,7 @@
         <v>430</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C13" s="39" t="s">
         <v>809</v>
@@ -22307,10 +22354,10 @@
         <v>454</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22318,18 +22365,18 @@
         <v>431</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="40" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C16" s="39" t="s">
         <v>808</v>
@@ -22337,10 +22384,10 @@
     </row>
     <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="40" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C17" s="39" t="s">
         <v>808</v>
@@ -22348,21 +22395,21 @@
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="40" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="40" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C19" s="39" t="s">
         <v>808</v>
@@ -22370,10 +22417,10 @@
     </row>
     <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="40" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>808</v>
@@ -22381,10 +22428,10 @@
     </row>
     <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="40" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>808</v>
@@ -22392,10 +22439,10 @@
     </row>
     <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="40" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C22" s="39" t="s">
         <v>808</v>
@@ -22403,54 +22450,54 @@
     </row>
     <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="40" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="40" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="40" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="40" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="40" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C27" s="39" t="s">
         <v>808</v>
@@ -22458,21 +22505,21 @@
     </row>
     <row r="28" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="40" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="40" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C29" s="39" t="s">
         <v>808</v>
@@ -22483,10 +22530,10 @@
         <v>455</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22494,10 +22541,10 @@
         <v>456</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22505,10 +22552,10 @@
         <v>457</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22516,18 +22563,18 @@
         <v>458</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="40" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C34" s="39" t="s">
         <v>808</v>
@@ -22535,10 +22582,10 @@
     </row>
     <row r="35" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="40" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C35" s="39" t="s">
         <v>808</v>
@@ -22546,10 +22593,10 @@
     </row>
     <row r="36" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="40" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C36" s="39" t="s">
         <v>808</v>
@@ -22557,10 +22604,10 @@
     </row>
     <row r="37" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="40" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C37" s="39" t="s">
         <v>808</v>
@@ -22568,10 +22615,10 @@
     </row>
     <row r="38" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="40" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C38" s="39" t="s">
         <v>808</v>
@@ -22582,10 +22629,10 @@
         <v>415</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22593,10 +22640,10 @@
         <v>432</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22604,10 +22651,10 @@
         <v>459</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22615,10 +22662,10 @@
         <v>460</v>
       </c>
       <c r="B42" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22626,10 +22673,10 @@
         <v>433</v>
       </c>
       <c r="B43" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C43" s="39" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22637,10 +22684,10 @@
         <v>462</v>
       </c>
       <c r="B44" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22648,7 +22695,7 @@
         <v>499</v>
       </c>
       <c r="B45" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C45" s="39" t="s">
         <v>808</v>
@@ -22656,10 +22703,10 @@
     </row>
     <row r="46" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="40" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C46" s="39" t="s">
         <v>808</v>
@@ -22667,10 +22714,10 @@
     </row>
     <row r="47" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="40" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B47" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C47" s="39" t="s">
         <v>808</v>
@@ -22678,10 +22725,10 @@
     </row>
     <row r="48" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="40" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C48" s="39" t="s">
         <v>808</v>
@@ -22692,10 +22739,10 @@
         <v>434</v>
       </c>
       <c r="B49" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C49" s="39" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22703,10 +22750,10 @@
         <v>463</v>
       </c>
       <c r="B50" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22714,7 +22761,7 @@
         <v>417</v>
       </c>
       <c r="B51" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C51" s="39" t="s">
         <v>807</v>
@@ -22725,7 +22772,7 @@
         <v>420</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C52" s="39" t="s">
         <v>807</v>
@@ -22733,10 +22780,10 @@
     </row>
     <row r="53" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="40" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C53" s="39" t="s">
         <v>808</v>
@@ -22747,7 +22794,7 @@
         <v>418</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C54" s="39" t="s">
         <v>807</v>
@@ -22758,7 +22805,7 @@
         <v>752</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C55" s="39" t="s">
         <v>806</v>
@@ -22769,7 +22816,7 @@
         <v>419</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C56" s="39" t="s">
         <v>807</v>
@@ -22780,7 +22827,7 @@
         <v>421</v>
       </c>
       <c r="B57" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C57" s="39" t="s">
         <v>807</v>
@@ -22791,10 +22838,10 @@
         <v>435</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22802,7 +22849,7 @@
         <v>763</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C59" s="39" t="s">
         <v>808</v>
@@ -22813,10 +22860,10 @@
         <v>464</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C60" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22824,10 +22871,10 @@
         <v>465</v>
       </c>
       <c r="B61" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C61" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22835,10 +22882,10 @@
         <v>466</v>
       </c>
       <c r="B62" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C62" s="39" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22846,10 +22893,10 @@
         <v>437</v>
       </c>
       <c r="B63" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C63" s="39" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22857,7 +22904,7 @@
         <v>436</v>
       </c>
       <c r="B64" s="40" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C64" s="39" t="s">
         <v>809</v>
@@ -22871,7 +22918,7 @@
         <v>439</v>
       </c>
       <c r="B66" s="40" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C66" s="39" t="s">
         <v>809</v>
@@ -22882,7 +22929,7 @@
         <v>441</v>
       </c>
       <c r="B67" s="40" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C67" s="39" t="s">
         <v>809</v>
@@ -22893,7 +22940,7 @@
     </row>
     <row r="69" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" s="40" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B69" s="40" t="s">
         <v>803</v>
@@ -22904,27 +22951,27 @@
     </row>
     <row r="70" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="40" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="B70" s="40" t="s">
         <v>803</v>
       </c>
       <c r="C70" s="39" t="s">
-        <v>1242</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C71" s="39"/>
     </row>
-    <row r="72" spans="1:3" ht="187" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="204" x14ac:dyDescent="0.2">
       <c r="A72" s="40" t="s">
         <v>438</v>
       </c>
       <c r="B72" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C72" s="39" t="s">
-        <v>1245</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22932,10 +22979,10 @@
         <v>470</v>
       </c>
       <c r="B73" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C73" s="39" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="68" x14ac:dyDescent="0.2">
@@ -22943,10 +22990,10 @@
         <v>592</v>
       </c>
       <c r="B74" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C74" s="39" t="s">
-        <v>1246</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="68" x14ac:dyDescent="0.2">
@@ -22954,10 +23001,10 @@
         <v>593</v>
       </c>
       <c r="B75" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C75" s="39" t="s">
-        <v>1246</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="68" x14ac:dyDescent="0.2">
@@ -22965,10 +23012,10 @@
         <v>594</v>
       </c>
       <c r="B76" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>1246</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="68" x14ac:dyDescent="0.2">
@@ -22976,10 +23023,10 @@
         <v>595</v>
       </c>
       <c r="B77" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C77" s="39" t="s">
-        <v>1246</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="68" x14ac:dyDescent="0.2">
@@ -22987,10 +23034,10 @@
         <v>596</v>
       </c>
       <c r="B78" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C78" s="39" t="s">
-        <v>1246</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -22998,10 +23045,10 @@
         <v>590</v>
       </c>
       <c r="B79" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C79" s="39" t="s">
-        <v>1247</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23009,10 +23056,10 @@
         <v>591</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>1248</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23020,10 +23067,10 @@
         <v>597</v>
       </c>
       <c r="B81" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C81" s="39" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23031,10 +23078,10 @@
         <v>598</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C82" s="39" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23042,10 +23089,10 @@
         <v>600</v>
       </c>
       <c r="B83" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C83" s="39" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23053,10 +23100,10 @@
         <v>599</v>
       </c>
       <c r="B84" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C84" s="39" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23064,10 +23111,10 @@
         <v>601</v>
       </c>
       <c r="B85" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C85" s="39" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23075,10 +23122,10 @@
         <v>602</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C86" s="39" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23086,21 +23133,21 @@
         <v>603</v>
       </c>
       <c r="B87" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C87" s="39" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="40" t="s">
         <v>604</v>
       </c>
       <c r="B88" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C88" s="39" t="s">
-        <v>1251</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23108,10 +23155,10 @@
         <v>605</v>
       </c>
       <c r="B89" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C89" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23119,10 +23166,10 @@
         <v>606</v>
       </c>
       <c r="B90" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C90" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23130,10 +23177,10 @@
         <v>607</v>
       </c>
       <c r="B91" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C91" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23141,10 +23188,10 @@
         <v>608</v>
       </c>
       <c r="B92" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C92" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23152,10 +23199,10 @@
         <v>609</v>
       </c>
       <c r="B93" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C93" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23163,10 +23210,10 @@
         <v>610</v>
       </c>
       <c r="B94" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C94" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23174,10 +23221,10 @@
         <v>611</v>
       </c>
       <c r="B95" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C95" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23185,10 +23232,10 @@
         <v>612</v>
       </c>
       <c r="B96" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C96" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23196,10 +23243,10 @@
         <v>613</v>
       </c>
       <c r="B97" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C97" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23207,10 +23254,10 @@
         <v>614</v>
       </c>
       <c r="B98" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C98" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23218,10 +23265,10 @@
         <v>615</v>
       </c>
       <c r="B99" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C99" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23229,10 +23276,10 @@
         <v>616</v>
       </c>
       <c r="B100" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C100" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23240,10 +23287,10 @@
         <v>617</v>
       </c>
       <c r="B101" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C101" s="39" t="s">
-        <v>1252</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23251,10 +23298,10 @@
         <v>716</v>
       </c>
       <c r="B102" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C102" s="39" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="34" x14ac:dyDescent="0.2">
@@ -23262,10 +23309,10 @@
         <v>717</v>
       </c>
       <c r="B103" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C103" s="39" t="s">
-        <v>1253</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23273,10 +23320,10 @@
         <v>624</v>
       </c>
       <c r="B104" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C104" s="39" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23284,7 +23331,7 @@
         <v>625</v>
       </c>
       <c r="B105" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C105" s="39" t="s">
         <v>806</v>
@@ -23295,7 +23342,7 @@
         <v>626</v>
       </c>
       <c r="B106" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C106" s="39" t="s">
         <v>806</v>
@@ -23306,7 +23353,7 @@
         <v>627</v>
       </c>
       <c r="B107" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C107" s="39" t="s">
         <v>806</v>
@@ -23317,7 +23364,7 @@
         <v>628</v>
       </c>
       <c r="B108" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C108" s="39" t="s">
         <v>806</v>
@@ -23328,7 +23375,7 @@
         <v>629</v>
       </c>
       <c r="B109" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C109" s="39" t="s">
         <v>806</v>
@@ -23339,7 +23386,7 @@
         <v>630</v>
       </c>
       <c r="B110" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C110" s="39" t="s">
         <v>806</v>
@@ -23350,7 +23397,7 @@
         <v>631</v>
       </c>
       <c r="B111" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C111" s="39" t="s">
         <v>806</v>
@@ -23361,7 +23408,7 @@
         <v>632</v>
       </c>
       <c r="B112" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C112" s="39" t="s">
         <v>806</v>
@@ -23372,7 +23419,7 @@
         <v>633</v>
       </c>
       <c r="B113" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C113" s="39" t="s">
         <v>806</v>
@@ -23383,7 +23430,7 @@
         <v>634</v>
       </c>
       <c r="B114" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C114" s="39" t="s">
         <v>806</v>
@@ -23394,7 +23441,7 @@
         <v>635</v>
       </c>
       <c r="B115" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C115" s="39" t="s">
         <v>806</v>
@@ -23405,7 +23452,7 @@
         <v>636</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C116" s="39" t="s">
         <v>806</v>
@@ -23416,7 +23463,7 @@
         <v>637</v>
       </c>
       <c r="B117" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C117" s="39" t="s">
         <v>806</v>
@@ -23427,7 +23474,7 @@
         <v>638</v>
       </c>
       <c r="B118" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C118" s="39" t="s">
         <v>806</v>
@@ -23438,7 +23485,7 @@
         <v>639</v>
       </c>
       <c r="B119" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C119" s="39" t="s">
         <v>806</v>
@@ -23449,7 +23496,7 @@
         <v>640</v>
       </c>
       <c r="B120" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C120" s="39" t="s">
         <v>806</v>
@@ -23460,7 +23507,7 @@
         <v>641</v>
       </c>
       <c r="B121" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C121" s="39" t="s">
         <v>806</v>
@@ -23471,10 +23518,10 @@
         <v>642</v>
       </c>
       <c r="B122" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C122" s="39" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23482,10 +23529,10 @@
         <v>643</v>
       </c>
       <c r="B123" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C123" s="39" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23493,10 +23540,10 @@
         <v>644</v>
       </c>
       <c r="B124" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C124" s="39" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23504,7 +23551,7 @@
         <v>645</v>
       </c>
       <c r="B125" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C125" s="39" t="s">
         <v>806</v>
@@ -23515,7 +23562,7 @@
         <v>646</v>
       </c>
       <c r="B126" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C126" s="39" t="s">
         <v>806</v>
@@ -23526,7 +23573,7 @@
         <v>647</v>
       </c>
       <c r="B127" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C127" s="39" t="s">
         <v>806</v>
@@ -23537,7 +23584,7 @@
         <v>648</v>
       </c>
       <c r="B128" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C128" s="39" t="s">
         <v>806</v>
@@ -23548,10 +23595,10 @@
         <v>649</v>
       </c>
       <c r="B129" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C129" s="39" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23559,10 +23606,10 @@
         <v>650</v>
       </c>
       <c r="B130" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C130" s="39" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23570,7 +23617,7 @@
         <v>651</v>
       </c>
       <c r="B131" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C131" s="39" t="s">
         <v>806</v>
@@ -23581,7 +23628,7 @@
         <v>652</v>
       </c>
       <c r="B132" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C132" s="39" t="s">
         <v>806</v>
@@ -23592,7 +23639,7 @@
         <v>653</v>
       </c>
       <c r="B133" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C133" s="39" t="s">
         <v>806</v>
@@ -23603,10 +23650,10 @@
         <v>654</v>
       </c>
       <c r="B134" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C134" s="39" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23614,10 +23661,10 @@
         <v>655</v>
       </c>
       <c r="B135" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C135" s="39" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23625,7 +23672,7 @@
         <v>656</v>
       </c>
       <c r="B136" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C136" s="39" t="s">
         <v>806</v>
@@ -23636,10 +23683,10 @@
         <v>657</v>
       </c>
       <c r="B137" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C137" s="39" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23647,7 +23694,7 @@
         <v>658</v>
       </c>
       <c r="B138" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C138" s="39" t="s">
         <v>806</v>
@@ -23658,10 +23705,10 @@
         <v>659</v>
       </c>
       <c r="B139" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C139" s="39" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23669,7 +23716,7 @@
         <v>660</v>
       </c>
       <c r="B140" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C140" s="39" t="s">
         <v>806</v>
@@ -23680,7 +23727,7 @@
         <v>661</v>
       </c>
       <c r="B141" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C141" s="39" t="s">
         <v>806</v>
@@ -23691,7 +23738,7 @@
         <v>662</v>
       </c>
       <c r="B142" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C142" s="39" t="s">
         <v>806</v>
@@ -23702,7 +23749,7 @@
         <v>663</v>
       </c>
       <c r="B143" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C143" s="39" t="s">
         <v>806</v>
@@ -23713,10 +23760,10 @@
         <v>664</v>
       </c>
       <c r="B144" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C144" s="39" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23724,7 +23771,7 @@
         <v>665</v>
       </c>
       <c r="B145" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C145" s="39" t="s">
         <v>806</v>
@@ -23735,10 +23782,10 @@
         <v>666</v>
       </c>
       <c r="B146" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C146" s="39" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23746,7 +23793,7 @@
         <v>667</v>
       </c>
       <c r="B147" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C147" s="39" t="s">
         <v>806</v>
@@ -23757,7 +23804,7 @@
         <v>668</v>
       </c>
       <c r="B148" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C148" s="39" t="s">
         <v>806</v>
@@ -23768,10 +23815,10 @@
         <v>669</v>
       </c>
       <c r="B149" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C149" s="39" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23779,7 +23826,7 @@
         <v>670</v>
       </c>
       <c r="B150" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C150" s="39" t="s">
         <v>806</v>
@@ -23790,10 +23837,10 @@
         <v>671</v>
       </c>
       <c r="B151" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C151" s="39" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23801,10 +23848,10 @@
         <v>672</v>
       </c>
       <c r="B152" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C152" s="39" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23812,10 +23859,10 @@
         <v>673</v>
       </c>
       <c r="B153" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C153" s="39" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23823,7 +23870,7 @@
         <v>674</v>
       </c>
       <c r="B154" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C154" s="39" t="s">
         <v>806</v>
@@ -23834,7 +23881,7 @@
         <v>675</v>
       </c>
       <c r="B155" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C155" s="39" t="s">
         <v>806</v>
@@ -23845,7 +23892,7 @@
         <v>676</v>
       </c>
       <c r="B156" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C156" s="39" t="s">
         <v>806</v>
@@ -23856,7 +23903,7 @@
         <v>677</v>
       </c>
       <c r="B157" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C157" s="39" t="s">
         <v>806</v>
@@ -23867,7 +23914,7 @@
         <v>678</v>
       </c>
       <c r="B158" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C158" s="39" t="s">
         <v>806</v>
@@ -23878,7 +23925,7 @@
         <v>679</v>
       </c>
       <c r="B159" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C159" s="39" t="s">
         <v>806</v>
@@ -23889,7 +23936,7 @@
         <v>680</v>
       </c>
       <c r="B160" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C160" s="39" t="s">
         <v>806</v>
@@ -23900,7 +23947,7 @@
         <v>681</v>
       </c>
       <c r="B161" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C161" s="39" t="s">
         <v>806</v>
@@ -23911,7 +23958,7 @@
         <v>682</v>
       </c>
       <c r="B162" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C162" s="39" t="s">
         <v>806</v>
@@ -23922,7 +23969,7 @@
         <v>683</v>
       </c>
       <c r="B163" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C163" s="39" t="s">
         <v>806</v>
@@ -23933,7 +23980,7 @@
         <v>684</v>
       </c>
       <c r="B164" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C164" s="39" t="s">
         <v>806</v>
@@ -23944,10 +23991,10 @@
         <v>685</v>
       </c>
       <c r="B165" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C165" s="39" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23955,7 +24002,7 @@
         <v>686</v>
       </c>
       <c r="B166" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C166" s="39" t="s">
         <v>806</v>
@@ -23966,10 +24013,10 @@
         <v>687</v>
       </c>
       <c r="B167" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C167" s="39" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23977,10 +24024,10 @@
         <v>688</v>
       </c>
       <c r="B168" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C168" s="39" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -23988,7 +24035,7 @@
         <v>689</v>
       </c>
       <c r="B169" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C169" s="39" t="s">
         <v>806</v>
@@ -23999,7 +24046,7 @@
         <v>690</v>
       </c>
       <c r="B170" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C170" s="39" t="s">
         <v>806</v>
@@ -24010,7 +24057,7 @@
         <v>691</v>
       </c>
       <c r="B171" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C171" s="39" t="s">
         <v>806</v>
@@ -24021,7 +24068,7 @@
         <v>692</v>
       </c>
       <c r="B172" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C172" s="39" t="s">
         <v>806</v>
@@ -24032,7 +24079,7 @@
         <v>693</v>
       </c>
       <c r="B173" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C173" s="39" t="s">
         <v>806</v>
@@ -24043,7 +24090,7 @@
         <v>694</v>
       </c>
       <c r="B174" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C174" s="39" t="s">
         <v>806</v>
@@ -24054,7 +24101,7 @@
         <v>695</v>
       </c>
       <c r="B175" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C175" s="39" t="s">
         <v>806</v>
@@ -24065,7 +24112,7 @@
         <v>696</v>
       </c>
       <c r="B176" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C176" s="39" t="s">
         <v>806</v>
@@ -24076,10 +24123,10 @@
         <v>697</v>
       </c>
       <c r="B177" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C177" s="39" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -24087,7 +24134,7 @@
         <v>698</v>
       </c>
       <c r="B178" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C178" s="39" t="s">
         <v>806</v>
@@ -24098,7 +24145,7 @@
         <v>699</v>
       </c>
       <c r="B179" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C179" s="39" t="s">
         <v>806</v>
@@ -24109,7 +24156,7 @@
         <v>700</v>
       </c>
       <c r="B180" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C180" s="39" t="s">
         <v>806</v>
@@ -24120,10 +24167,10 @@
         <v>618</v>
       </c>
       <c r="B181" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C181" s="39" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -24131,10 +24178,10 @@
         <v>701</v>
       </c>
       <c r="B182" s="40" t="s">
+        <v>839</v>
+      </c>
+      <c r="C182" s="39" t="s">
         <v>840</v>
-      </c>
-      <c r="C182" s="39" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -24142,10 +24189,10 @@
         <v>702</v>
       </c>
       <c r="B183" s="40" t="s">
+        <v>839</v>
+      </c>
+      <c r="C183" s="39" t="s">
         <v>840</v>
-      </c>
-      <c r="C183" s="39" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -24153,7 +24200,7 @@
         <v>757</v>
       </c>
       <c r="B184" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C184" s="39" t="s">
         <v>808</v>
@@ -24164,7 +24211,7 @@
         <v>758</v>
       </c>
       <c r="B185" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C185" s="39" t="s">
         <v>808</v>
@@ -24175,7 +24222,7 @@
         <v>760</v>
       </c>
       <c r="B186" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C186" s="39" t="s">
         <v>808</v>
@@ -24186,7 +24233,7 @@
         <v>761</v>
       </c>
       <c r="B187" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C187" s="39" t="s">
         <v>808</v>
@@ -24197,7 +24244,7 @@
         <v>762</v>
       </c>
       <c r="B188" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C188" s="39" t="s">
         <v>808</v>
@@ -24208,7 +24255,7 @@
         <v>763</v>
       </c>
       <c r="B189" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C189" s="39" t="s">
         <v>808</v>
@@ -24219,7 +24266,7 @@
         <v>764</v>
       </c>
       <c r="B190" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C190" s="39" t="s">
         <v>808</v>
@@ -24230,7 +24277,7 @@
         <v>765</v>
       </c>
       <c r="B191" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C191" s="39" t="s">
         <v>808</v>
@@ -24241,7 +24288,7 @@
         <v>766</v>
       </c>
       <c r="B192" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C192" s="39" t="s">
         <v>808</v>
@@ -24252,7 +24299,7 @@
         <v>767</v>
       </c>
       <c r="B193" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C193" s="39" t="s">
         <v>808</v>
@@ -24263,7 +24310,7 @@
         <v>768</v>
       </c>
       <c r="B194" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C194" s="39" t="s">
         <v>808</v>
@@ -24274,7 +24321,7 @@
         <v>769</v>
       </c>
       <c r="B195" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C195" s="39" t="s">
         <v>808</v>
@@ -24285,7 +24332,7 @@
         <v>770</v>
       </c>
       <c r="B196" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C196" s="39" t="s">
         <v>808</v>
@@ -24296,7 +24343,7 @@
         <v>771</v>
       </c>
       <c r="B197" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C197" s="39" t="s">
         <v>808</v>
@@ -24307,7 +24354,7 @@
         <v>772</v>
       </c>
       <c r="B198" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C198" s="39" t="s">
         <v>808</v>
@@ -24318,7 +24365,7 @@
         <v>773</v>
       </c>
       <c r="B199" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C199" s="39" t="s">
         <v>808</v>
@@ -24329,7 +24376,7 @@
         <v>774</v>
       </c>
       <c r="B200" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C200" s="39" t="s">
         <v>808</v>
@@ -24340,7 +24387,7 @@
         <v>775</v>
       </c>
       <c r="B201" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C201" s="39" t="s">
         <v>808</v>
@@ -24351,7 +24398,7 @@
         <v>776</v>
       </c>
       <c r="B202" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C202" s="39" t="s">
         <v>808</v>
@@ -24362,7 +24409,7 @@
         <v>777</v>
       </c>
       <c r="B203" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C203" s="39" t="s">
         <v>808</v>
@@ -24373,7 +24420,7 @@
         <v>778</v>
       </c>
       <c r="B204" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C204" s="39" t="s">
         <v>808</v>
@@ -24384,7 +24431,7 @@
         <v>779</v>
       </c>
       <c r="B205" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C205" s="39" t="s">
         <v>808</v>
@@ -24392,68 +24439,68 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" s="40" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B206" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C206" s="40" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" s="40" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B207" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C207" s="40" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" s="40" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B208" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C208" s="40" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="40" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B209" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C209" s="40" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="40" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B210" s="40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C210" s="40" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="40" t="s">
+        <v>919</v>
+      </c>
+      <c r="B211" s="40" t="s">
+        <v>839</v>
+      </c>
+      <c r="C211" s="40" t="s">
         <v>920</v>
-      </c>
-      <c r="B211" s="40" t="s">
-        <v>840</v>
-      </c>
-      <c r="C211" s="40" t="s">
-        <v>921</v>
       </c>
     </row>
   </sheetData>
@@ -24683,7 +24730,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C1" s="50"/>
       <c r="D1" s="50"/>
@@ -24714,7 +24761,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C3" t="s">
         <v>468</v>
@@ -24728,7 +24775,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C4" t="s">
         <v>339</v>
@@ -24742,10 +24789,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C5" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>562</v>
@@ -24756,13 +24803,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C6" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>1170</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1171</v>
       </c>
       <c r="E6" t="s">
         <v>481</v>
@@ -24770,13 +24817,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>1172</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1173</v>
       </c>
       <c r="E7" t="s">
         <v>480</v>
@@ -24784,18 +24831,18 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>1174</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C9" t="s">
         <v>502</v>
@@ -24806,7 +24853,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C10" t="s">
         <v>341</v>
@@ -24817,7 +24864,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C11" t="s">
         <v>586</v>
@@ -24864,7 +24911,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C1" s="49"/>
       <c r="D1" s="49"/>
@@ -24889,16 +24936,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>117</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>407</v>
@@ -24906,7 +24953,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="29"/>
@@ -24919,7 +24966,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="27" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="29"/>
@@ -24930,7 +24977,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="27" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="29"/>
@@ -24939,88 +24986,88 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
   </sheetData>
@@ -25057,7 +25104,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C1" s="51"/>
       <c r="D1" s="51"/>
@@ -25082,16 +25129,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E3" t="s">
         <v>407</v>
@@ -25099,14 +25146,14 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="36" t="s">
+        <v>901</v>
+      </c>
+      <c r="D4" s="36" t="s">
         <v>902</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>903</v>
       </c>
       <c r="E4" t="s">
         <v>408</v>
@@ -25114,14 +25161,14 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="35" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="36" t="s">
+        <v>903</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>904</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>905</v>
       </c>
       <c r="E5" t="s">
         <v>409</v>
@@ -25129,14 +25176,14 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="35" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="36" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E6" t="s">
         <v>480</v>
@@ -25144,7 +25191,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="35" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B7" s="3"/>
       <c r="D7" s="4"/>
@@ -25154,41 +25201,41 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="35" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B8" s="3"/>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="35" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B9" s="3"/>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="35" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="35" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="35" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="35" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="35" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -25225,7 +25272,7 @@
         <v>390</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="C1" s="52"/>
       <c r="D1" s="52"/>
@@ -25250,10 +25297,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="43" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="C3" t="s">
         <v>117</v>
@@ -25267,7 +25314,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>118</v>
@@ -25278,7 +25325,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="28" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" t="s">
@@ -25558,15 +25605,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D3C69E808006664F9CCA3D9BC71AC55D" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b5845cacad74656bcde11e00306ad31f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d75e0231-c5c8-4c84-8215-b760034bdfa5" xmlns:ns4="621de0e2-4b56-4c44-bb0f-ce9b0aec4994" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2cb8dbf20762a8ba415eee6dfba6bc92" ns3:_="" ns4:_="">
     <xsd:import namespace="d75e0231-c5c8-4c84-8215-b760034bdfa5"/>
@@ -25819,6 +25857,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -25828,14 +25875,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41548EA-A522-4942-9ABF-935FDE65872B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B426DB6-4B6A-4971-948B-870FFF62E8F5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25850,6 +25889,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41548EA-A522-4942-9ABF-935FDE65872B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/TBM Organization Parameters.xlsx
+++ b/TBM Organization Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/MicroDrive/SparrowGIT/TBM_Organization_Parameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E8A5F7-EFBF-2A44-807D-9D23A20B5129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE922174-C818-3745-9266-4E1D3CA987CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" tabRatio="813" firstSheet="26" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" tabRatio="813" firstSheet="18" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TBM" sheetId="7" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4920" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="1317">
   <si>
     <t>Latitude</t>
   </si>
@@ -4462,6 +4462,9 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4470,9 +4473,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4963,13 +4963,13 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -5136,12 +5136,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>394</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -5281,12 +5281,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>395</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -5599,12 +5599,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>396</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -5733,12 +5733,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1257</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -5853,12 +5853,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>397</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -6495,12 +6495,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>398</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -7035,12 +7035,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -7331,12 +7331,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>399</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -7571,12 +7571,12 @@
       <c r="A1" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1308</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -7605,10 +7605,10 @@
       <c r="A3" s="14" t="s">
         <v>1310</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="50" t="s">
         <v>900</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="50" t="s">
         <v>900</v>
       </c>
       <c r="E3" s="40" t="s">
@@ -7619,10 +7619,10 @@
       <c r="A4" s="14" t="s">
         <v>1311</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="50" t="s">
         <v>901</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="50" t="s">
         <v>1314</v>
       </c>
       <c r="E4" s="40" t="s">
@@ -7630,7 +7630,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="50" t="s">
         <v>1312</v>
       </c>
       <c r="E5" s="40" t="s">
@@ -7638,7 +7638,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="50" t="s">
         <v>1313</v>
       </c>
       <c r="E6" s="40" t="s">
@@ -7674,12 +7674,12 @@
       <c r="A1" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>997</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -7714,15 +7714,24 @@
       <c r="D3" t="s">
         <v>469</v>
       </c>
+      <c r="E3" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
         <v>955</v>
       </c>
+      <c r="E4" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>956</v>
+      </c>
+      <c r="E5" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -8320,6 +8329,18 @@
     <mergeCell ref="B1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{48150005-A7B8-E545-BB29-25304312CBE5}">
+          <x14:formula1>
+            <xm:f>Validation!$B$1:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E5</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -8337,12 +8358,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>391</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -8511,12 +8532,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="52" t="s">
         <v>1017</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -8697,12 +8718,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="52" t="s">
         <v>1048</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -8922,12 +8943,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>848</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -9251,12 +9272,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>400</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -9508,12 +9529,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -9684,12 +9705,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>402</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -10061,12 +10082,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>405</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -10177,12 +10198,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>923</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -10407,12 +10428,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>922</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -10609,12 +10630,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>404</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -10762,12 +10783,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>392</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="20" t="s">
@@ -10963,12 +10984,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1244</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -11081,12 +11102,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>876</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -11280,12 +11301,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -11450,12 +11471,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>403</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -11623,12 +11644,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1258</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -11876,12 +11897,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1103</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -12112,12 +12133,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1104</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -12353,12 +12374,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1246</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -12536,12 +12557,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -21632,12 +21653,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>703</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -21909,12 +21930,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1098</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -22045,12 +22066,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>1099</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -24864,12 +24885,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="52" t="s">
         <v>1167</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -25045,12 +25066,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>854</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -25238,12 +25259,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>887</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -25406,12 +25427,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="54" t="s">
         <v>1233</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -25576,12 +25597,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>393</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -25740,23 +25761,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d75e0231-c5c8-4c84-8215-b760034bdfa5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D3C69E808006664F9CCA3D9BC71AC55D" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b5845cacad74656bcde11e00306ad31f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d75e0231-c5c8-4c84-8215-b760034bdfa5" xmlns:ns4="621de0e2-4b56-4c44-bb0f-ce9b0aec4994" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2cb8dbf20762a8ba415eee6dfba6bc92" ns3:_="" ns4:_="">
     <xsd:import namespace="d75e0231-c5c8-4c84-8215-b760034bdfa5"/>
@@ -26009,10 +26013,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d75e0231-c5c8-4c84-8215-b760034bdfa5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41548EA-A522-4942-9ABF-935FDE65872B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B426DB6-4B6A-4971-948B-870FFF62E8F5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d75e0231-c5c8-4c84-8215-b760034bdfa5"/>
+    <ds:schemaRef ds:uri="621de0e2-4b56-4c44-bb0f-ce9b0aec4994"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -26035,20 +26067,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B426DB6-4B6A-4971-948B-870FFF62E8F5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41548EA-A522-4942-9ABF-935FDE65872B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d75e0231-c5c8-4c84-8215-b760034bdfa5"/>
-    <ds:schemaRef ds:uri="621de0e2-4b56-4c44-bb0f-ce9b0aec4994"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/TBM Organization Parameters.xlsx
+++ b/TBM Organization Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/MicroDrive/SparrowGIT/TBM_Organization_Parameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE922174-C818-3745-9266-4E1D3CA987CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F591CBA-E276-8E47-9A8D-9C611461A0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" tabRatio="813" firstSheet="18" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" tabRatio="813" firstSheet="22" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TBM" sheetId="7" r:id="rId1"/>
@@ -54,13 +54,15 @@
     <sheet name="WiFi_Languages" sheetId="33" state="hidden" r:id="rId39"/>
     <sheet name="IPMRP" sheetId="45" r:id="rId40"/>
     <sheet name="IPMRN" sheetId="46" r:id="rId41"/>
-    <sheet name="Wifi_Materials" sheetId="37" r:id="rId42"/>
-    <sheet name="Wifi_Downloads" sheetId="38" r:id="rId43"/>
-    <sheet name="Validation" sheetId="34" state="hidden" r:id="rId44"/>
-    <sheet name="Data Valid" sheetId="2" state="hidden" r:id="rId45"/>
+    <sheet name="PMGPE" sheetId="56" r:id="rId42"/>
+    <sheet name="PMGPW" sheetId="57" r:id="rId43"/>
+    <sheet name="Wifi_Materials" sheetId="37" r:id="rId44"/>
+    <sheet name="Wifi_Downloads" sheetId="38" r:id="rId45"/>
+    <sheet name="Validation" sheetId="34" state="hidden" r:id="rId46"/>
+    <sheet name="Data Valid" sheetId="2" state="hidden" r:id="rId47"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId46"/>
+    <externalReference r:id="rId48"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">WiFi_Languages!$A$1:$D$636</definedName>
@@ -100,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4985" uniqueCount="1333">
   <si>
     <t>Latitude</t>
   </si>
@@ -4052,19 +4054,74 @@
   </si>
   <si>
     <t>TBM, TBMAR, TBMCV, TBMKA, TBMK, TBMPB, TBMKB, TBMSL, TBMGN, TBMSA, TBMKN, TBMPM</t>
+  </si>
+  <si>
+    <t>Pioneer Mission Global - East Pokot</t>
+  </si>
+  <si>
+    <t>Tangulbei</t>
+  </si>
+  <si>
+    <t>Chemolingot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pokot </t>
+  </si>
+  <si>
+    <t>Luyha</t>
+  </si>
+  <si>
+    <t>Dholuo</t>
+  </si>
+  <si>
+    <t>Gikuyu</t>
+  </si>
+  <si>
+    <t>Pioneer Mission Global - West Pokot</t>
+  </si>
+  <si>
+    <t>Serewo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohifong </t>
+  </si>
+  <si>
+    <t>Nakohigu fong</t>
+  </si>
+  <si>
+    <t>Nayili fong North</t>
+  </si>
+  <si>
+    <t>Nayili fong South</t>
+  </si>
+  <si>
+    <t>Kalli fong</t>
+  </si>
+  <si>
+    <t>Kpatuli fong</t>
+  </si>
+  <si>
+    <t>Kuga fong</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4357,112 +4414,112 @@
   </borders>
   <cellStyleXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="31" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="30" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4472,9 +4529,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="14">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7004,7 +7063,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -10071,7 +10130,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9796B9BC-A579-4EDE-99EB-40D54CC290A0}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -10107,8 +10166,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
-        <v>1212</v>
+      <c r="A3" s="11" t="s">
+        <v>1330</v>
       </c>
       <c r="B3" t="s">
         <v>117</v>
@@ -10124,8 +10183,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="18" t="s">
-        <v>1213</v>
+      <c r="A4" s="11" t="s">
+        <v>1331</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="18"/>
@@ -10134,8 +10193,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
-        <v>1214</v>
+      <c r="A5" s="11" t="s">
+        <v>1332</v>
       </c>
       <c r="B5" s="3"/>
       <c r="D5" s="18"/>
@@ -10144,26 +10203,57 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
-        <v>1215</v>
+      <c r="A6" s="11" t="s">
+        <v>1326</v>
       </c>
       <c r="B6" s="2"/>
       <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
+      <c r="A7" s="11" t="s">
+        <v>1327</v>
+      </c>
       <c r="B7" s="3"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>1328</v>
+      </c>
       <c r="B8" s="3"/>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>1329</v>
+      </c>
       <c r="B9" s="3"/>
       <c r="D9" s="4"/>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="18" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="18" t="s">
+        <v>1215</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A13">
+    <sortCondition ref="A3:A13"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
@@ -10175,7 +10265,7 @@
           <x14:formula1>
             <xm:f>Validation!$B$1:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>E4:E1048576 E3</xm:sqref>
+          <xm:sqref>E3:E1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -21901,7 +21991,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -22194,6 +22284,293 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{395B706A-E337-434F-B496-90FED3D131D8}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="G1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>505</v>
+      </c>
+      <c r="E3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" t="s">
+        <v>471</v>
+      </c>
+      <c r="D4" t="s">
+        <v>471</v>
+      </c>
+      <c r="E4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+      <c r="C5" t="s">
+        <v>478</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>478</v>
+      </c>
+      <c r="E5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="2"/>
+      <c r="C6" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4F7BD4-E599-3A48-912C-5B28C4454E56}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="G1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>505</v>
+      </c>
+      <c r="E3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="3"/>
+      <c r="C4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>478</v>
+      </c>
+      <c r="E4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+      <c r="C5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="2"/>
+      <c r="C6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD4090C0-81F3-488A-BFE0-128FBADFA632}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -22351,7 +22728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B17A051-E04F-4C5E-BBD2-8BC11DFBB7DE}">
   <dimension ref="A1:C211"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -24673,7 +25050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0388E7-6D7C-494A-B5B0-A06D9161366A}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -24727,7 +25104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -26014,20 +26391,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d75e0231-c5c8-4c84-8215-b760034bdfa5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d75e0231-c5c8-4c84-8215-b760034bdfa5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26050,6 +26427,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41548EA-A522-4942-9ABF-935FDE65872B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B09A22F1-B742-4DEC-998C-03DEA5FA7C76}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -26064,12 +26449,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41548EA-A522-4942-9ABF-935FDE65872B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/TBM Organization Parameters.xlsx
+++ b/TBM Organization Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/MicroDrive/SparrowGIT/TBM_Organization_Parameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8134AAC5-2FFF-724B-B926-874643E1E131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB3647F-0B8B-B142-9433-257F25B24AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" tabRatio="813" firstSheet="7" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20420" tabRatio="813" firstSheet="6" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TBM" sheetId="7" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5028" uniqueCount="1352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5029" uniqueCount="1353">
   <si>
     <t>Latitude</t>
   </si>
@@ -4162,6 +4162,9 @@
   </si>
   <si>
     <t>Lázaro Cárdenas</t>
+  </si>
+  <si>
+    <t>Bangkers</t>
   </si>
 </sst>
 </file>
@@ -4584,13 +4587,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -7931,6 +7934,9 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="40" t="s">
+        <v>1352</v>
+      </c>
       <c r="C5" s="50" t="s">
         <v>1312</v>
       </c>
@@ -8147,12 +8153,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="53" t="s">
         <v>1017</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -8333,12 +8339,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="53" t="s">
         <v>1343</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -8448,12 +8454,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="53" t="s">
         <v>1048</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -9484,12 +9490,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="55" t="s">
         <v>405</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -25619,12 +25625,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="53" t="s">
         <v>1167</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
       <c r="F1" s="19" t="s">
         <v>495</v>
       </c>
@@ -25993,12 +25999,12 @@
       <c r="A1" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="55" t="s">
         <v>887</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -26495,15 +26501,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D3C69E808006664F9CCA3D9BC71AC55D" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b5845cacad74656bcde11e00306ad31f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d75e0231-c5c8-4c84-8215-b760034bdfa5" xmlns:ns4="621de0e2-4b56-4c44-bb0f-ce9b0aec4994" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2cb8dbf20762a8ba415eee6dfba6bc92" ns3:_="" ns4:_="">
     <xsd:import namespace="d75e0231-c5c8-4c84-8215-b760034bdfa5"/>
@@ -26756,7 +26753,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="d75e0231-c5c8-4c84-8215-b760034bdfa5" xsi:nil="true"/>
@@ -26764,15 +26761,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41548EA-A522-4942-9ABF-935FDE65872B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B426DB6-4B6A-4971-948B-870FFF62E8F5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26791,7 +26789,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B09A22F1-B742-4DEC-998C-03DEA5FA7C76}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -26806,4 +26804,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F41548EA-A522-4942-9ABF-935FDE65872B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>